--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__E_Max.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__E_Max.xlsx
@@ -381,689 +381,689 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.1458</v>
+        <v>0.1508</v>
       </c>
       <c r="C2">
-        <v>0.09329999999999999</v>
+        <v>0.7745</v>
       </c>
       <c r="D2">
-        <v>0.02695</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.113</v>
+        <v>0.2541</v>
       </c>
       <c r="C3">
-        <v>0.1762</v>
+        <v>0.472</v>
       </c>
       <c r="D3">
-        <v>0.05185</v>
+        <v>0.21225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.373</v>
+        <v>0.1014</v>
       </c>
       <c r="C4">
-        <v>0.4618</v>
+        <v>0.1492</v>
       </c>
       <c r="D4">
-        <v>0.2101</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.2114</v>
+        <v>0.9307</v>
       </c>
       <c r="C5">
-        <v>0.5924</v>
+        <v>0.5641</v>
       </c>
       <c r="D5">
-        <v>0.26415</v>
+        <v>0.35245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.1014</v>
+        <v>0.1252</v>
       </c>
       <c r="C6">
-        <v>0.1492</v>
+        <v>0.2608</v>
       </c>
       <c r="D6">
-        <v>0.0625</v>
+        <v>0.10205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.2541</v>
+        <v>0.9455</v>
       </c>
       <c r="C7">
-        <v>0.472</v>
+        <v>0.7297</v>
       </c>
       <c r="D7">
-        <v>0.21225</v>
+        <v>0.14325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.6526999999999999</v>
+        <v>0.5162</v>
       </c>
       <c r="C8">
-        <v>0.6264</v>
+        <v>0.628</v>
       </c>
       <c r="D8">
-        <v>0.1416</v>
+        <v>0.3396</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.0607</v>
+        <v>0.7437</v>
       </c>
       <c r="C9">
-        <v>0.4296</v>
+        <v>0.6613</v>
       </c>
       <c r="D9">
-        <v>0.01375</v>
+        <v>0.3066</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.3529</v>
+        <v>0.1054</v>
       </c>
       <c r="C10">
-        <v>0.4861</v>
+        <v>0.0987</v>
       </c>
       <c r="D10">
-        <v>0.17275</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.9455</v>
+        <v>0.1458</v>
       </c>
       <c r="C11">
-        <v>0.7297</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="D11">
-        <v>0.14325</v>
+        <v>0.02695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.1252</v>
+        <v>0.2337</v>
       </c>
       <c r="C12">
-        <v>0.2608</v>
+        <v>0.2457</v>
       </c>
       <c r="D12">
-        <v>0.10205</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1508</v>
+        <v>0.0982</v>
       </c>
       <c r="C13">
-        <v>0.7745</v>
+        <v>0.1199</v>
       </c>
       <c r="D13">
-        <v>0.0684</v>
+        <v>0.01475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.9077</v>
+        <v>0.1128</v>
       </c>
       <c r="C14">
-        <v>0.2427</v>
+        <v>0.1507</v>
       </c>
       <c r="D14">
-        <v>0.00455</v>
+        <v>0.06665</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.9086</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="C15">
-        <v>0.1992</v>
+        <v>0.1176</v>
       </c>
       <c r="D15">
-        <v>0.01545</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16">
-        <v>1.1</v>
+        <v>0.0607</v>
       </c>
       <c r="C16">
-        <v>0.0863</v>
+        <v>0.4296</v>
       </c>
       <c r="D16">
-        <v>0.0235</v>
+        <v>0.01375</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.9163</v>
+        <v>0.1513</v>
       </c>
       <c r="C17">
-        <v>0.8645</v>
+        <v>0.1236</v>
       </c>
       <c r="D17">
-        <v>0.03815</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.1054</v>
+        <v>0.0958</v>
       </c>
       <c r="C18">
-        <v>0.0987</v>
+        <v>0.1469</v>
       </c>
       <c r="D18">
-        <v>0.0177</v>
+        <v>0.11085</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.0348</v>
+        <v>1.001</v>
       </c>
       <c r="C19">
-        <v>0.1573</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="D19">
-        <v>0.0015</v>
+        <v>0.51705</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.09279999999999999</v>
+        <v>0.8204</v>
       </c>
       <c r="C20">
-        <v>0.1278</v>
+        <v>1.0031</v>
       </c>
       <c r="D20">
-        <v>0.03885</v>
+        <v>0.0973</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.1156</v>
+        <v>0.1482</v>
       </c>
       <c r="C21">
-        <v>0.1744</v>
+        <v>0.2337</v>
       </c>
       <c r="D21">
-        <v>0.009600000000000001</v>
+        <v>0.09425</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.2337</v>
+        <v>0.3529</v>
       </c>
       <c r="C22">
-        <v>0.2457</v>
+        <v>0.4861</v>
       </c>
       <c r="D22">
-        <v>0.1037</v>
+        <v>0.17275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.5162</v>
+        <v>0.373</v>
       </c>
       <c r="C23">
-        <v>0.628</v>
+        <v>0.4618</v>
       </c>
       <c r="D23">
-        <v>0.3396</v>
+        <v>0.2101</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.5705</v>
+        <v>0.9163</v>
       </c>
       <c r="C24">
-        <v>0.0819</v>
+        <v>0.8645</v>
       </c>
       <c r="D24">
-        <v>0.0706</v>
+        <v>0.03815</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.09229999999999999</v>
+        <v>0.2284</v>
       </c>
       <c r="C25">
-        <v>0.2399</v>
+        <v>0.5416</v>
       </c>
       <c r="D25">
-        <v>0.10345</v>
+        <v>0.00535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.0354</v>
+        <v>0.7958</v>
       </c>
       <c r="C26">
-        <v>0.0495</v>
+        <v>0.8623</v>
       </c>
       <c r="D26">
-        <v>0.0126</v>
+        <v>0.41595</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.0743</v>
+        <v>0.2114</v>
       </c>
       <c r="C27">
-        <v>0.0441</v>
+        <v>0.5924</v>
       </c>
       <c r="D27">
-        <v>0.013</v>
+        <v>0.26415</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.2284</v>
+        <v>0.0354</v>
       </c>
       <c r="C28">
-        <v>0.5416</v>
+        <v>0.0495</v>
       </c>
       <c r="D28">
-        <v>0.00535</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.7958</v>
+        <v>0.9086</v>
       </c>
       <c r="C29">
-        <v>0.8623</v>
+        <v>0.1992</v>
       </c>
       <c r="D29">
-        <v>0.41595</v>
+        <v>0.01545</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.0982</v>
+        <v>0.1518</v>
       </c>
       <c r="C30">
-        <v>0.1199</v>
+        <v>0.2221</v>
       </c>
       <c r="D30">
-        <v>0.01475</v>
+        <v>0.15615</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.1128</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="C31">
-        <v>0.1507</v>
+        <v>0.6264</v>
       </c>
       <c r="D31">
-        <v>0.06665</v>
+        <v>0.1416</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.0958</v>
+        <v>0.1295</v>
       </c>
       <c r="C32">
-        <v>0.1469</v>
+        <v>0.4069</v>
       </c>
       <c r="D32">
-        <v>0.11085</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.1518</v>
+        <v>0.0348</v>
       </c>
       <c r="C33">
-        <v>0.2221</v>
+        <v>0.1573</v>
       </c>
       <c r="D33">
-        <v>0.15615</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.2399</v>
+        <v>0.9077</v>
       </c>
       <c r="C34">
-        <v>0.2887</v>
+        <v>0.2427</v>
       </c>
       <c r="D34">
-        <v>0.04615</v>
+        <v>0.00455</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.1295</v>
+        <v>0.1156</v>
       </c>
       <c r="C35">
-        <v>0.4069</v>
+        <v>0.1744</v>
       </c>
       <c r="D35">
-        <v>0.1161</v>
+        <v>0.009600000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.09329999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="C36">
-        <v>0.1176</v>
+        <v>0.1762</v>
       </c>
       <c r="D36">
-        <v>0.0078</v>
+        <v>0.05185</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.8204</v>
+        <v>0.2399</v>
       </c>
       <c r="C37">
-        <v>1.0031</v>
+        <v>0.2887</v>
       </c>
       <c r="D37">
-        <v>0.0973</v>
+        <v>0.04615</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38">
-        <v>1.001</v>
+        <v>1.1</v>
       </c>
       <c r="C38">
-        <v>0.8008999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="D38">
-        <v>0.51705</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.1796</v>
+        <v>0.4363</v>
       </c>
       <c r="C39">
-        <v>0.2221</v>
+        <v>0.7087</v>
       </c>
       <c r="D39">
-        <v>0.15145</v>
+        <v>0.2499</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.4363</v>
+        <v>0.5705</v>
       </c>
       <c r="C40">
-        <v>0.7087</v>
+        <v>0.0819</v>
       </c>
       <c r="D40">
-        <v>0.2499</v>
+        <v>0.0706</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.1513</v>
+        <v>0.1796</v>
       </c>
       <c r="C41">
-        <v>0.1236</v>
+        <v>0.2221</v>
       </c>
       <c r="D41">
-        <v>0.08</v>
+        <v>0.15145</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.9307</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="C42">
-        <v>0.5641</v>
+        <v>0.1278</v>
       </c>
       <c r="D42">
-        <v>0.35245</v>
+        <v>0.03885</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.1482</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C43">
-        <v>0.2337</v>
+        <v>0.2399</v>
       </c>
       <c r="D43">
-        <v>0.09425</v>
+        <v>0.10345</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.7437</v>
+        <v>0.0743</v>
       </c>
       <c r="C44">
-        <v>0.6613</v>
+        <v>0.0441</v>
       </c>
       <c r="D44">
-        <v>0.3066</v>
+        <v>0.013</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1091,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1535,7 +1535,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
